--- a/data_processed/Indicators_Banks_clean.xlsx
+++ b/data_processed/Indicators_Banks_clean.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>loans_to_clients</t>
+          <t>loans</t>
         </is>
       </c>
     </row>
